--- a/data/other.xlsx
+++ b/data/other.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94468aa6da851130/Desktop/reto/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="8_{4A01A130-6556-4F98-B72F-6A37BEB5EA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{622EDC74-61BD-4CC4-8817-BD69E9646444}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="8_{4A01A130-6556-4F98-B72F-6A37BEB5EA4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACB7D485-C147-4C79-95E8-FAAC3A294930}"/>
   <bookViews>
-    <workbookView xWindow="14880" yWindow="3015" windowWidth="11265" windowHeight="11865" xr2:uid="{0F4B6587-F1F7-42E2-B62E-5FCFE2E0452F}"/>
+    <workbookView xWindow="2160" yWindow="5220" windowWidth="14535" windowHeight="10230" xr2:uid="{0F4B6587-F1F7-42E2-B62E-5FCFE2E0452F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -855,9 +855,6 @@
     <t>写真 ポーチ集め</t>
   </si>
   <si>
-    <t>ひばり</t>
-  </si>
-  <si>
     <t>ファッション 食べ歩き</t>
   </si>
   <si>
@@ -1741,9 +1738,6 @@
     <t>ニュー・ウィッチ・ベロ号</t>
   </si>
   <si>
-    <t>モビーディック号</t>
-  </si>
-  <si>
     <t>カラス丸</t>
   </si>
   <si>
@@ -2135,6 +2129,17 @@
   </si>
   <si>
     <t>ベラミー海賊団　船</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モビー・ディック号</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ひばり 趣味</t>
+    <rPh sb="4" eb="6">
+      <t>シュミ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2200,6 +2205,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3611,7 +3620,7 @@
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>273</v>
+        <v>646</v>
       </c>
       <c r="B139" t="s">
         <v>272</v>
@@ -3619,63 +3628,63 @@
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B140" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B141" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B142" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B143" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B144" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B145" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B146" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B147" t="s">
         <v>64</v>
@@ -3683,119 +3692,119 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B148" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B149" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B150" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B151" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B152" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B153" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B154" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B155" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B156" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B157" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B158" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B159" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B160" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B161" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B162" t="s">
         <v>228</v>
@@ -3803,167 +3812,167 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B163" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B164" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B165" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B166" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B167" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B168" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B169" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B170" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B171" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A172" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B172" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A173" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B173" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B174" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B175" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B176" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B177" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B178" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B179" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B180" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B181" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B182" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B183" t="s">
         <v>167</v>
@@ -3971,447 +3980,447 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B184" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B185" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B186" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B187" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B188" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B189" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B190" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B191" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B192" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B193" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B194" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B195" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B196" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B197" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B198" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B199" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A200" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B200" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B201" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B202" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B203" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A204" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B204" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B205" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B206" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A207" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B207" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B208" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B209" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B210" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B211" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B212" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B213" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B214" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A215" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B215" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B216" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B217" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A218" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B218" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B219" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B220" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B221" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B222" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B223" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B224" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B225" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B226" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A227" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B227" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B228" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B229" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A230" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B230" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A231" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B231" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A232" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B232" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A233" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B233" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A234" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B234" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A235" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B235" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A236" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B236" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A237" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B237" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A238" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B238" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A239" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B239" t="s">
         <v>159</v>
@@ -4419,730 +4428,730 @@
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A240" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B240" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A241" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B241" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A242" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B242" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A243" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B243" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A244" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B244" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A245" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B245" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A246" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B246" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A247" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B247" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A248" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B248" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A249" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B249" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A250" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B250" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A251" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B251" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A252" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B252" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A253" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B253" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A254" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B254" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A255" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B255" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A256" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B256" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A257" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B257" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A258" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B258" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A259" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B259" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A260" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B260" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A261" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B261" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A262" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B262" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A263" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B263" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A264" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B264" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A265" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B265" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A266" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B266" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A267" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B267" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A268" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B268" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A269" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B269" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A270" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B270" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A271" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B271" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A272" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B272" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A273" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B273" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A274" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B274" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A275" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B275" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A276" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B276" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A277" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B277" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A278" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="B278" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A279" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B279" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A280" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="B280" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A281" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B281" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A282" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B282" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A283" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B283" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A284" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B284" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A285" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B285" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A286" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B286" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A287" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B287" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A288" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B288" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A289" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B289" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A290" t="s">
+        <v>643</v>
+      </c>
+      <c r="B290" t="s">
         <v>645</v>
-      </c>
-      <c r="B290" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A291" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B291" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A292" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B292" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A293" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B293" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A294" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B294" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A295" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B295" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A296" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B296" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A297" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B297" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A298" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B298" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A299" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B299" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A300" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B300" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A301" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B301" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A302" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B302" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A303" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B303" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A304" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B304" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A305" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B305" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A306" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B306" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A307" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B307" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A308" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B308" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A309" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B309" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A310" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B310" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A311" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B311" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A312" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B312" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A313" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B313" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A314" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B314" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A315" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B315" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A316" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B316" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A317" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B317" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A318" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B318" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A319" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B319" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A320" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B320" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A321" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B321" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A322" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B322" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A323" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B323" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A324" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B324" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A325" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B325" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A326" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B326" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A327" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B327" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A328" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B328" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A329" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B329" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A330" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B330" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
   </sheetData>
